--- a/inputs/styles_cross.xlsx
+++ b/inputs/styles_cross.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="styles" sheetId="1" r:id="Rf6c0e9c6a0474590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="styles" sheetId="1" r:id="R61e16358ae3d4517"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1872,6 +1872,14 @@
         <x:v>Stouts+Porters</x:v>
       </x:c>
     </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>Mild - Other</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>Ales - Other</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
